--- a/artfynd/A 26143-2024 artfynd.xlsx
+++ b/artfynd/A 26143-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127158235</v>
       </c>
       <c r="B2" t="n">
-        <v>79059</v>
+        <v>79090</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>127158223</v>
       </c>
       <c r="B3" t="n">
-        <v>91210</v>
+        <v>91284</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>127158412</v>
       </c>
       <c r="B4" t="n">
-        <v>78386</v>
+        <v>78417</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 26143-2024 artfynd.xlsx
+++ b/artfynd/A 26143-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127158235</v>
       </c>
       <c r="B2" t="n">
-        <v>79090</v>
+        <v>79093</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>127158223</v>
       </c>
       <c r="B3" t="n">
-        <v>91284</v>
+        <v>91290</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>127158412</v>
       </c>
       <c r="B4" t="n">
-        <v>78417</v>
+        <v>78420</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 26143-2024 artfynd.xlsx
+++ b/artfynd/A 26143-2024 artfynd.xlsx
@@ -775,7 +775,7 @@
         <v>127158223</v>
       </c>
       <c r="B3" t="n">
-        <v>91290</v>
+        <v>91291</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 26143-2024 artfynd.xlsx
+++ b/artfynd/A 26143-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127158235</v>
       </c>
       <c r="B2" t="n">
-        <v>79093</v>
+        <v>79097</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>127158223</v>
       </c>
       <c r="B3" t="n">
-        <v>91291</v>
+        <v>91295</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>127158412</v>
       </c>
       <c r="B4" t="n">
-        <v>78420</v>
+        <v>78424</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 26143-2024 artfynd.xlsx
+++ b/artfynd/A 26143-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127158235</v>
       </c>
       <c r="B2" t="n">
-        <v>79097</v>
+        <v>79099</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>127158223</v>
       </c>
       <c r="B3" t="n">
-        <v>91295</v>
+        <v>91297</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>127158412</v>
       </c>
       <c r="B4" t="n">
-        <v>78424</v>
+        <v>78426</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 26143-2024 artfynd.xlsx
+++ b/artfynd/A 26143-2024 artfynd.xlsx
@@ -775,7 +775,7 @@
         <v>127158223</v>
       </c>
       <c r="B3" t="n">
-        <v>91297</v>
+        <v>91303</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 26143-2024 artfynd.xlsx
+++ b/artfynd/A 26143-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127158235</v>
       </c>
       <c r="B2" t="n">
-        <v>79099</v>
+        <v>79102</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>127158223</v>
       </c>
       <c r="B3" t="n">
-        <v>91303</v>
+        <v>91306</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>127158412</v>
       </c>
       <c r="B4" t="n">
-        <v>78426</v>
+        <v>78429</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 26143-2024 artfynd.xlsx
+++ b/artfynd/A 26143-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127158235</v>
       </c>
       <c r="B2" t="n">
-        <v>79102</v>
+        <v>79108</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>127158223</v>
       </c>
       <c r="B3" t="n">
-        <v>91306</v>
+        <v>91314</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>127158412</v>
       </c>
       <c r="B4" t="n">
-        <v>78429</v>
+        <v>78435</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 26143-2024 artfynd.xlsx
+++ b/artfynd/A 26143-2024 artfynd.xlsx
@@ -775,7 +775,7 @@
         <v>127158223</v>
       </c>
       <c r="B3" t="n">
-        <v>91314</v>
+        <v>91315</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 26143-2024 artfynd.xlsx
+++ b/artfynd/A 26143-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127158235</v>
       </c>
       <c r="B2" t="n">
-        <v>79108</v>
+        <v>79090</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>127158223</v>
       </c>
       <c r="B3" t="n">
-        <v>91315</v>
+        <v>91284</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>127158412</v>
       </c>
       <c r="B4" t="n">
-        <v>78435</v>
+        <v>78417</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 26143-2024 artfynd.xlsx
+++ b/artfynd/A 26143-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127158235</v>
       </c>
       <c r="B2" t="n">
-        <v>79090</v>
+        <v>79108</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>127158223</v>
       </c>
       <c r="B3" t="n">
-        <v>91284</v>
+        <v>91315</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>127158412</v>
       </c>
       <c r="B4" t="n">
-        <v>78417</v>
+        <v>78435</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 26143-2024 artfynd.xlsx
+++ b/artfynd/A 26143-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127158235</v>
       </c>
       <c r="B2" t="n">
-        <v>79108</v>
+        <v>79406</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>127158223</v>
       </c>
       <c r="B3" t="n">
-        <v>91315</v>
+        <v>91872</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>127158412</v>
       </c>
       <c r="B4" t="n">
-        <v>78435</v>
+        <v>78730</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 26143-2024 artfynd.xlsx
+++ b/artfynd/A 26143-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127158235</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127158223</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,8 +978,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127158412</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>